--- a/voting/022_voting_for_finalists--voting.xlsx
+++ b/voting/022_voting_for_finalists--voting.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voting For Finalists</t>
+          <t>Select Your Vote</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Voting For Finalists</t>
+          <t>Describe Your Preferences</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vote</t>
+          <t>Date of Vote</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vote</t>
+          <t>Time of Vote</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vote</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voting For Finalists</t>
+          <t>Rating 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Voting For Finalists</t>
+          <t>Rating 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vote</t>
+          <t>Select Multiple Options</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vote</t>
+          <t>Vote for Group</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vote</t>
+          <t>Voting For Finalists Page 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Voting For Finalists</t>
+          <t>Voting For Finalists Page 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Voting For Finalists</t>
+          <t>Thoughts</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -849,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>voting_for_finalists_page_8_choices</t>
+          <t>voting_for_finalists_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i'm_not_sure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I'm Not Sure</t>
         </is>
       </c>
     </row>
@@ -883,29 +883,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>voting_for_finalists_page_9_choices</t>
+          <t>voting_for_finalists_page_8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -917,29 +917,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>voting_for_finalists_page_10_choices</t>
+          <t>voting_for_finalists_page_9_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -951,29 +951,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>voting_for_finalists_page_11_choices</t>
+          <t>voting_for_finalists_page_10_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>voting_for_finalists_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
